--- a/data/trans_orig/P05A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338603</t>
+          <t>331807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390642</t>
+          <t>387154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297868</t>
+          <t>299042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>350860</t>
+          <t>352283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>648976</t>
+          <t>647406</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>724799</t>
+          <t>719899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255839</t>
+          <t>257427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306666</t>
+          <t>312181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272950</t>
+          <t>272899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322436</t>
+          <t>323370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542555</t>
+          <t>546017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>614896</t>
+          <t>618085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63920</t>
+          <t>64336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51548</t>
+          <t>51735</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81466</t>
+          <t>83648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98895</t>
+          <t>97856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>138612</t>
+          <t>137827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493280</t>
+          <t>491432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>555037</t>
+          <t>556002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>51,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>505810</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>475160</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>534911</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>52,23%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>49,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>55,24%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1029340</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>990338</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1078744</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>53,35%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>51,33%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>57,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>505810</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471686</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>536786</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>52,23%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>55,43%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1029340</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>982968</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1073341</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>53,35%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>50,95%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>320688</t>
+          <t>322707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>381164</t>
+          <t>380517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>310728</t>
+          <t>309549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>372373</t>
+          <t>367728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>649359</t>
+          <t>642597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>733118</t>
+          <t>728156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>69038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105744</t>
+          <t>105344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106463</t>
+          <t>104561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146771</t>
+          <t>146812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184718</t>
+          <t>183489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241414</t>
+          <t>240039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>326086</t>
+          <t>326680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>380983</t>
+          <t>379459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359298</t>
+          <t>358004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>410846</t>
+          <t>408412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>703951</t>
+          <t>699678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>773991</t>
+          <t>771972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216905</t>
+          <t>216123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267527</t>
+          <t>268872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196734</t>
+          <t>195772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>244929</t>
+          <t>244604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>426975</t>
+          <t>430362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>496904</t>
+          <t>497680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>63963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100940</t>
+          <t>101465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92067</t>
+          <t>93162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132959</t>
+          <t>133789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>184635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>464387</t>
+          <t>463437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>524734</t>
+          <t>521998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>452382</t>
+          <t>451721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>517220</t>
+          <t>515977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>931511</t>
+          <t>934322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1021159</t>
+          <t>1028324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>312976</t>
+          <t>309364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370093</t>
+          <t>367502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>332997</t>
+          <t>332894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397507</t>
+          <t>396950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>660055</t>
+          <t>655701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>747380</t>
+          <t>743680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89939</t>
+          <t>91246</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129642</t>
+          <t>130699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163197</t>
+          <t>163958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212766</t>
+          <t>213396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264158</t>
+          <t>265348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329815</t>
+          <t>327106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1671918</t>
+          <t>1671606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1787667</t>
+          <t>1788804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1640577</t>
+          <t>1638876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1756357</t>
+          <t>1753476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3356520</t>
+          <t>3340558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3518119</t>
+          <t>3503987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1164232</t>
+          <t>1162947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1277100</t>
+          <t>1272086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1168636</t>
+          <t>1168849</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1280920</t>
+          <t>1275453</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2359015</t>
+          <t>2360398</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2512847</t>
+          <t>2519056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>296613</t>
+          <t>293495</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>362488</t>
+          <t>362341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>414955</t>
+          <t>420122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>495318</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>723227</t>
+          <t>734002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>836954</t>
+          <t>836581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>519286</t>
+          <t>522462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>565238</t>
+          <t>566040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>515691</t>
+          <t>514461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>562211</t>
+          <t>560027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1050216</t>
+          <t>1048251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1112866</t>
+          <t>1112640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118268</t>
+          <t>119201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162707</t>
+          <t>160192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111536</t>
+          <t>112955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>156154</t>
+          <t>155599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244609</t>
+          <t>244956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>303988</t>
+          <t>306793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34969</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55748</t>
+          <t>54065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>711318</t>
+          <t>711567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>769802</t>
+          <t>770312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>709054</t>
+          <t>711966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>773766</t>
+          <t>770283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1439013</t>
+          <t>1443491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1524048</t>
+          <t>1528108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>205627</t>
+          <t>205661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>263258</t>
+          <t>259077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>209099</t>
+          <t>211948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>266737</t>
+          <t>265179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433440</t>
+          <t>430991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>510840</t>
+          <t>510815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>55498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66586</t>
+          <t>67451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73392</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112539</t>
+          <t>110622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>484140</t>
+          <t>483358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>537614</t>
+          <t>538683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>508145</t>
+          <t>511680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>561958</t>
+          <t>564592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1012490</t>
+          <t>1010910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1086667</t>
+          <t>1080668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166857</t>
+          <t>168985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215420</t>
+          <t>220926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156133</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205775</t>
+          <t>202836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338223</t>
+          <t>336642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403048</t>
+          <t>406008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39738</t>
+          <t>39876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72366</t>
+          <t>69813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77291</t>
+          <t>77818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95259</t>
+          <t>97520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138943</t>
+          <t>140192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>511302</t>
+          <t>510609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>573416</t>
+          <t>572999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>642333</t>
+          <t>645926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>708169</t>
+          <t>709187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1172465</t>
+          <t>1176019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1265020</t>
+          <t>1270141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269889</t>
+          <t>270885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330787</t>
+          <t>331043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>242673</t>
+          <t>246178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>301014</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,47 +4776,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>28,88%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>572407</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>527120</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>611433</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>28,64%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>572407</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>528963</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>615334</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>28,64%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>85961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124427</t>
+          <t>127514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>83928</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120909</t>
+          <t>124291</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>180218</t>
+          <t>179090</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235465</t>
+          <t>234149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2282682</t>
+          <t>2286459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2396489</t>
+          <t>2394117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2439274</t>
+          <t>2435719</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2549770</t>
+          <t>2551859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4760047</t>
+          <t>4765199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4918867</t>
+          <t>4919501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>815909</t>
+          <t>813418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>918403</t>
+          <t>917529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>773161</t>
+          <t>767178</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>874913</t>
+          <t>872355</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1611615</t>
+          <t>1614482</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1756750</t>
+          <t>1749883</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186662</t>
+          <t>188398</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245324</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>206727</t>
+          <t>209362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>268851</t>
+          <t>271966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>407652</t>
+          <t>411313</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>495291</t>
+          <t>501099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>541885</t>
+          <t>544087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>581840</t>
+          <t>582930</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>540684</t>
+          <t>540655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>579822</t>
+          <t>580479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1094220</t>
+          <t>1096154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1152577</t>
+          <t>1151249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75385</t>
+          <t>74806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111917</t>
+          <t>109834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,82 +5885,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>84009</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66939</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101272</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>174730</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>150460</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>198201</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84009</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67341</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>101191</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>174730</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>150353</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>202638</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>37067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34842</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62904</t>
+          <t>61218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>735628</t>
+          <t>734701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>791688</t>
+          <t>793485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>771794</t>
+          <t>771952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>826432</t>
+          <t>825344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1524195</t>
+          <t>1525825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1601851</t>
+          <t>1605365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186913</t>
+          <t>188018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241450</t>
+          <t>241862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>155938</t>
+          <t>155157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>205678</t>
+          <t>205285</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>356424</t>
+          <t>356730</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>430069</t>
+          <t>430658</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33431</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61819</t>
+          <t>59709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44697</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76676</t>
+          <t>78190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129781</t>
+          <t>127235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>453576</t>
+          <t>455355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>509807</t>
+          <t>511014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>446091</t>
+          <t>444411</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>499924</t>
+          <t>501499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>916059</t>
+          <t>909632</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>995382</t>
+          <t>992430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>203629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256703</t>
+          <t>255917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229272</t>
+          <t>228847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280105</t>
+          <t>281871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>449792</t>
+          <t>452711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523091</t>
+          <t>528762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>59804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>43685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74982</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82977</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124036</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>568020</t>
+          <t>567828</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>627946</t>
+          <t>626718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>660344</t>
+          <t>659330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>722398</t>
+          <t>723386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1247713</t>
+          <t>1245838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1333180</t>
+          <t>1332167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>248559</t>
+          <t>247152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303083</t>
+          <t>303436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235606</t>
+          <t>233113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292423</t>
+          <t>292883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494133</t>
+          <t>499099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>576975</t>
+          <t>577905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49899</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81538</t>
+          <t>80647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68400</t>
+          <t>70835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106905</t>
+          <t>109338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130018</t>
+          <t>129721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179388</t>
+          <t>175642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2358398</t>
+          <t>2352354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2463259</t>
+          <t>2465028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2471081</t>
+          <t>2468133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2579615</t>
+          <t>2574743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4857914</t>
+          <t>4855485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5011271</t>
+          <t>5017726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>760183</t>
+          <t>760094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>856771</t>
+          <t>867740</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>731642</t>
+          <t>727895</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>830463</t>
+          <t>831038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1523261</t>
+          <t>1515835</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1665136</t>
+          <t>1664846</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149034</t>
+          <t>146103</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200082</t>
+          <t>198607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204263</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>261565</t>
+          <t>265938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364726</t>
+          <t>365690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446020</t>
+          <t>446835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>554603</t>
+          <t>554782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>588571</t>
+          <t>587722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>651728</t>
+          <t>652740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>682122</t>
+          <t>681557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1219105</t>
+          <t>1218060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1262540</t>
+          <t>1263683</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>35807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67414</t>
+          <t>67624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29924</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>73503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111183</t>
+          <t>113273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41894</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996115</t>
+          <t>990416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1113681</t>
+          <t>1121269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>768587</t>
+          <t>767845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>810249</t>
+          <t>809647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1777979</t>
+          <t>1779891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1940419</t>
+          <t>1942069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132659</t>
+          <t>132316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108551</t>
+          <t>110193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>147827</t>
+          <t>146870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>144239</t>
+          <t>148496</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>265754</t>
+          <t>263243</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81825</t>
+          <t>84885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62167</t>
+          <t>62250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123161</t>
+          <t>125784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498780</t>
+          <t>503336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>550537</t>
+          <t>552352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314990</t>
+          <t>282734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>743309</t>
+          <t>743972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>744760</t>
+          <t>731260</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1271423</t>
+          <t>1269387</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134480</t>
+          <t>133988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185418</t>
+          <t>180794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148944</t>
+          <t>149578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>596523</t>
+          <t>629753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308399</t>
+          <t>308668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>857794</t>
+          <t>863191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47561</t>
+          <t>46936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68097</t>
+          <t>68804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>549917</t>
+          <t>550142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>613945</t>
+          <t>611834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662481</t>
+          <t>659449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>775883</t>
+          <t>783468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1231859</t>
+          <t>1232925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1365309</t>
+          <t>1362293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>225906</t>
+          <t>229120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287354</t>
+          <t>287391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224666</t>
+          <t>220158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>311090</t>
+          <t>313974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>468806</t>
+          <t>473324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>575727</t>
+          <t>580146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71500</t>
+          <t>70181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110995</t>
+          <t>109547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91188</t>
+          <t>88508</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134832</t>
+          <t>135883</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171891</t>
+          <t>174440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232250</t>
+          <t>232821</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2648396</t>
+          <t>2644107</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2893326</t>
+          <t>2895736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2225091</t>
+          <t>2236442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2915021</t>
+          <t>2910916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4915344</t>
+          <t>4847633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5682650</t>
+          <t>5661836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>438998</t>
+          <t>433685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>621307</t>
+          <t>625530</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>587980</t>
+          <t>587837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1326205</t>
+          <t>1312426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1116765</t>
+          <t>1130477</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1950911</t>
+          <t>2068696</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131385</t>
+          <t>134441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>209956</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165751</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231197</t>
+          <t>230764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318560</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>428628</t>
+          <t>423616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>331807</t>
+          <t>335915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>387154</t>
+          <t>389403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>299042</t>
+          <t>296806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352283</t>
+          <t>347710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>647406</t>
+          <t>648882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>719899</t>
+          <t>723825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257427</t>
+          <t>256157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312181</t>
+          <t>306726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272899</t>
+          <t>273323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323370</t>
+          <t>324672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546017</t>
+          <t>547344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>618085</t>
+          <t>617175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>37823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64336</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51735</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>81240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97856</t>
+          <t>95194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>137827</t>
+          <t>135670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491432</t>
+          <t>489826</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>556002</t>
+          <t>554125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475160</t>
+          <t>474360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534911</t>
+          <t>537406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>990338</t>
+          <t>985198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1078744</t>
+          <t>1074266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>322707</t>
+          <t>319923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>380517</t>
+          <t>385218</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>309549</t>
+          <t>309009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>367728</t>
+          <t>365974</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>642597</t>
+          <t>647172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>728156</t>
+          <t>731346</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69038</t>
+          <t>69420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105344</t>
+          <t>107115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104561</t>
+          <t>104038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146812</t>
+          <t>144464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183489</t>
+          <t>183687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240039</t>
+          <t>240626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>326680</t>
+          <t>326611</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>379459</t>
+          <t>379610</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>358004</t>
+          <t>358529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>408412</t>
+          <t>410472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>699678</t>
+          <t>696967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>771972</t>
+          <t>774142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216123</t>
+          <t>218361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268872</t>
+          <t>270278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195772</t>
+          <t>196246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>244604</t>
+          <t>244605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>430362</t>
+          <t>429078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497680</t>
+          <t>498883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63963</t>
+          <t>66334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101465</t>
+          <t>101729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60386</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93162</t>
+          <t>92344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133789</t>
+          <t>132965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184635</t>
+          <t>182545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>463437</t>
+          <t>462598</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>521998</t>
+          <t>526189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>451721</t>
+          <t>451704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>515977</t>
+          <t>515483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>934322</t>
+          <t>927811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1028324</t>
+          <t>1021447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309364</t>
+          <t>309553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367502</t>
+          <t>367379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>332894</t>
+          <t>332714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396950</t>
+          <t>397190</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>655701</t>
+          <t>663539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>743680</t>
+          <t>750143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91246</t>
+          <t>90803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130699</t>
+          <t>129513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163958</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213396</t>
+          <t>215498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>265348</t>
+          <t>269041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>327106</t>
+          <t>329235</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1671606</t>
+          <t>1669534</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1788804</t>
+          <t>1783761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1638876</t>
+          <t>1638891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1753476</t>
+          <t>1756622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3340558</t>
+          <t>3349443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3503987</t>
+          <t>3512657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1162947</t>
+          <t>1164147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1272086</t>
+          <t>1273017</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1168849</t>
+          <t>1167324</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1275453</t>
+          <t>1277303</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2360398</t>
+          <t>2353486</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2519056</t>
+          <t>2514724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>293495</t>
+          <t>294368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>362341</t>
+          <t>363283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>420122</t>
+          <t>411152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>495299</t>
+          <t>493231</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>734002</t>
+          <t>734417</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>836581</t>
+          <t>837105</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>522462</t>
+          <t>517988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>566040</t>
+          <t>565389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>514461</t>
+          <t>515824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>560027</t>
+          <t>561469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1048251</t>
+          <t>1050484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1112640</t>
+          <t>1115670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119201</t>
+          <t>119121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>163280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112955</t>
+          <t>113360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>155599</t>
+          <t>156699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244956</t>
+          <t>240881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>306793</t>
+          <t>302697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>27047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34264</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54065</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>711567</t>
+          <t>712028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>770312</t>
+          <t>769893</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>711966</t>
+          <t>714525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>770283</t>
+          <t>770401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1443491</t>
+          <t>1439861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1528108</t>
+          <t>1528834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>205661</t>
+          <t>206393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>259077</t>
+          <t>262255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>211948</t>
+          <t>210957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>265179</t>
+          <t>265931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>430991</t>
+          <t>429804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>510815</t>
+          <t>513726</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29381</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55498</t>
+          <t>55685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>37344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>67642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>72334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110622</t>
+          <t>110805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>483358</t>
+          <t>484189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>538683</t>
+          <t>535444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>511680</t>
+          <t>507084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>564592</t>
+          <t>562874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1010910</t>
+          <t>1010690</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1080668</t>
+          <t>1088706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168985</t>
+          <t>167620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220926</t>
+          <t>217671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153667</t>
+          <t>156175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202836</t>
+          <t>206657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>336642</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>406008</t>
+          <t>403817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69813</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45784</t>
+          <t>45801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77818</t>
+          <t>77065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97520</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140192</t>
+          <t>140371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>510609</t>
+          <t>509489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>572999</t>
+          <t>571539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>645926</t>
+          <t>647247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>709187</t>
+          <t>709356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1176019</t>
+          <t>1176517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1270141</t>
+          <t>1265172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270885</t>
+          <t>270978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331043</t>
+          <t>330975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246178</t>
+          <t>246160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>302931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>527120</t>
+          <t>529354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>611433</t>
+          <t>614351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85961</t>
+          <t>86267</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127514</t>
+          <t>124523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83928</t>
+          <t>84004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124291</t>
+          <t>124770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179090</t>
+          <t>180068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>234149</t>
+          <t>233838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2286459</t>
+          <t>2290496</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2394117</t>
+          <t>2393800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2435719</t>
+          <t>2436516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2551859</t>
+          <t>2545187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4765199</t>
+          <t>4763795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4919501</t>
+          <t>4919165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>813418</t>
+          <t>812155</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>917529</t>
+          <t>910383</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>767178</t>
+          <t>773694</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>872355</t>
+          <t>878396</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1614482</t>
+          <t>1604287</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1749883</t>
+          <t>1753728</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188398</t>
+          <t>189308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>248313</t>
+          <t>248372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209362</t>
+          <t>208493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>271966</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>411313</t>
+          <t>413728</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>501099</t>
+          <t>499674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>544087</t>
+          <t>542951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>582930</t>
+          <t>582575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>540655</t>
+          <t>541120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>580479</t>
+          <t>579221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1096154</t>
+          <t>1095524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1151249</t>
+          <t>1153000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109834</t>
+          <t>110309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,82 +5885,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>84009</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67742</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>102027</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>174730</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>149274</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>200426</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>11,09%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84009</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66939</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>101272</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>174730</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>150460</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>198201</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31874</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>38055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>34288</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61218</t>
+          <t>61087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>734701</t>
+          <t>736006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>793485</t>
+          <t>793143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>771952</t>
+          <t>773798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>825344</t>
+          <t>829964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1525825</t>
+          <t>1524224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1605365</t>
+          <t>1605374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188018</t>
+          <t>188659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241862</t>
+          <t>241416</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>155157</t>
+          <t>154327</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>205285</t>
+          <t>205859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>356730</t>
+          <t>358037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>430658</t>
+          <t>429519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59709</t>
+          <t>59182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45868</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78190</t>
+          <t>76418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85424</t>
+          <t>84439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127235</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>455355</t>
+          <t>456416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>511014</t>
+          <t>511608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>444411</t>
+          <t>443749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>501499</t>
+          <t>499419</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>909632</t>
+          <t>914644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>992430</t>
+          <t>993951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>203629</t>
+          <t>205270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255917</t>
+          <t>256924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228847</t>
+          <t>228329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>281871</t>
+          <t>281320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>452711</t>
+          <t>452210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528762</t>
+          <t>528433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59804</t>
+          <t>56681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72965</t>
+          <t>73269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83197</t>
+          <t>82739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122928</t>
+          <t>122271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>567828</t>
+          <t>567989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>626718</t>
+          <t>626469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>659330</t>
+          <t>662193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>723386</t>
+          <t>723723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1245838</t>
+          <t>1247132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1332167</t>
+          <t>1333697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247152</t>
+          <t>248362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233113</t>
+          <t>234274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292883</t>
+          <t>290948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>499099</t>
+          <t>496301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>577905</t>
+          <t>579299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80647</t>
+          <t>83038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70835</t>
+          <t>70525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109338</t>
+          <t>109401</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129721</t>
+          <t>129758</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175642</t>
+          <t>177252</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2352354</t>
+          <t>2356632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2465028</t>
+          <t>2459967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2468133</t>
+          <t>2469825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2574743</t>
+          <t>2579641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4855485</t>
+          <t>4859903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5017726</t>
+          <t>5007627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>760094</t>
+          <t>761850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>867740</t>
+          <t>864703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>727895</t>
+          <t>730528</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>831038</t>
+          <t>833360</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1515835</t>
+          <t>1524787</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1664846</t>
+          <t>1660712</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146103</t>
+          <t>150494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198607</t>
+          <t>202754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204163</t>
+          <t>203539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265938</t>
+          <t>261542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>365690</t>
+          <t>368422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>444543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>573773</t>
+          <t>623399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>554782</t>
+          <t>605272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>587722</t>
+          <t>639425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>668390</t>
+          <t>671577</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>652740</t>
+          <t>654841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>681557</t>
+          <t>683104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1242163</t>
+          <t>1294976</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1218060</t>
+          <t>1271060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1263683</t>
+          <t>1315533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>54226</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67624</t>
+          <t>71659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>46206</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56294</t>
+          <t>59438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>100432</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73503</t>
+          <t>81266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113273</t>
+          <t>121169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>42177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1043466</t>
+          <t>879632</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>990416</t>
+          <t>849350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121269</t>
+          <t>905107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>789863</t>
+          <t>881310</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>767845</t>
+          <t>857682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>809647</t>
+          <t>904167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1833330</t>
+          <t>1760942</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1779891</t>
+          <t>1725376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1942069</t>
+          <t>1797029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97275</t>
+          <t>119776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>97280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132316</t>
+          <t>146329</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127428</t>
+          <t>141147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110193</t>
+          <t>121832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146870</t>
+          <t>163857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>224703</t>
+          <t>260923</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148496</t>
+          <t>230229</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>263243</t>
+          <t>296934</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84885</t>
+          <t>67211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>36991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>61238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>92012</t>
+          <t>96920</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125784</t>
+          <t>117028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957181</t>
+          <t>1069868</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957181</t>
+          <t>1069868</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957181</t>
+          <t>1069868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150045</t>
+          <t>2118785</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150045</t>
+          <t>2118785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150045</t>
+          <t>2118785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>527091</t>
+          <t>594921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>503336</t>
+          <t>565178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>552352</t>
+          <t>622193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>573014</t>
+          <t>626939</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>282734</t>
+          <t>602859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>743972</t>
+          <t>647762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1100104</t>
+          <t>1221861</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>731260</t>
+          <t>1185990</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1269387</t>
+          <t>1253614</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>157584</t>
+          <t>180729</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133988</t>
+          <t>156508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180794</t>
+          <t>210053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>328329</t>
+          <t>148153</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149578</t>
+          <t>128924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>629753</t>
+          <t>169411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>485913</t>
+          <t>328881</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308668</t>
+          <t>298019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>863191</t>
+          <t>363867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31301</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46936</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68804</t>
+          <t>80281</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>581930</t>
+          <t>613866</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>550142</t>
+          <t>582642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>611834</t>
+          <t>646663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>700140</t>
+          <t>680059</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>659449</t>
+          <t>650269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>783468</t>
+          <t>707024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1282070</t>
+          <t>1293925</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1232925</t>
+          <t>1247625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1362293</t>
+          <t>1339200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>255596</t>
+          <t>279838</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>229120</t>
+          <t>245854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287391</t>
+          <t>309601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>279169</t>
+          <t>307175</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>220158</t>
+          <t>282280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313974</t>
+          <t>336162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>534765</t>
+          <t>587013</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>473324</t>
+          <t>548086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>580146</t>
+          <t>628888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>94395</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70181</t>
+          <t>77103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109547</t>
+          <t>116659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>114274</t>
+          <t>130386</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88508</t>
+          <t>112648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>135883</t>
+          <t>152200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>202581</t>
+          <t>224781</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174440</t>
+          <t>194761</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232821</t>
+          <t>252325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925833</t>
+          <t>988099</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925833</t>
+          <t>988099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925833</t>
+          <t>988099</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1093583</t>
+          <t>1117620</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1093583</t>
+          <t>1117620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1093583</t>
+          <t>1117620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019416</t>
+          <t>2105719</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019416</t>
+          <t>2105719</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019416</t>
+          <t>2105719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2726260</t>
+          <t>2711819</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2644107</t>
+          <t>2656245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2895736</t>
+          <t>2766267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2731407</t>
+          <t>2859885</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2236442</t>
+          <t>2816900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2910916</t>
+          <t>2908734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5457668</t>
+          <t>5571703</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4847633</t>
+          <t>5495648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5661836</t>
+          <t>5640992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>559387</t>
+          <t>634569</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>433685</t>
+          <t>582326</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>625530</t>
+          <t>685706</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>776678</t>
+          <t>642681</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>587837</t>
+          <t>600008</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1312426</t>
+          <t>684501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1336065</t>
+          <t>1277250</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1130477</t>
+          <t>1212134</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2068696</t>
+          <t>1349294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>171987</t>
+          <t>182148</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134441</t>
+          <t>154177</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>209802</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,67 +10349,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>201375</t>
+          <t>231362</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163137</t>
+          <t>204668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>230764</t>
+          <t>258950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>413509</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>372918</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>451952</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>6,22%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>373362</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>314345</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>423616</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3457634</t>
+          <t>3528535</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3457634</t>
+          <t>3528535</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3457634</t>
+          <t>3528535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3709460</t>
+          <t>3733927</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3709460</t>
+          <t>3733927</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3709460</t>
+          <t>3733927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7167095</t>
+          <t>7262462</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7167095</t>
+          <t>7262462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7167095</t>
+          <t>7262462</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
